--- a/AAII_Financials/Yearly/TTNDY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TTNDY_YR_FIN.xlsx
@@ -2921,10 +2921,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4032700</v>
+        <v>1817300</v>
       </c>
       <c r="E57" s="3">
-        <v>3871000</v>
+        <v>1872300</v>
       </c>
       <c r="F57" s="3">
         <v>3391700</v>
@@ -3023,10 +3023,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>498500</v>
+        <v>2713900</v>
       </c>
       <c r="E59" s="3">
-        <v>384100</v>
+        <v>2382800</v>
       </c>
       <c r="F59" s="3">
         <v>315400</v>
